--- a/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69A67A68-45BB-45DD-85DE-A87F3D452E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC41EC3-99FB-4236-B88C-D969910B94E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C080BD3A-5C25-4F84-A05C-5AD866DA7A5B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9EE96E5C-9D83-4045-BEE7-43846A1B0312}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3025,7 +3025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D54C3875-4F0A-4260-B764-64F31F7F2CBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1EA03E-3944-4E8D-8CF6-CAB347F81A39}">
   <dimension ref="B3:L392"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC41EC3-99FB-4236-B88C-D969910B94E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61C46083-C4F6-444A-8277-BA2451505537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9EE96E5C-9D83-4045-BEE7-43846A1B0312}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DF5C930F-7F38-4A09-A858-E97568083CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3025,7 +3025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1EA03E-3944-4E8D-8CF6-CAB347F81A39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C580CE-EAAB-4568-83A9-6AC6E3E052BA}">
   <dimension ref="B3:L392"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1AFF80-107E-41E8-8B20-A8B002E113F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A69376B-E70B-4887-93C7-9EE93191A0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C914E550-2E49-48D3-80A2-B0ED31ECEC10}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CFE364B3-C1DF-4EFA-A808-2E62F5B9BF6B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -925,7 +925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D3E46E-69DC-4F85-A915-B06761397502}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EE2903-FC55-46D2-B322-9AD334A84B5A}">
   <dimension ref="B3:L65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A69376B-E70B-4887-93C7-9EE93191A0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF87C421-066E-4A14-8A81-12F640D3FDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CFE364B3-C1DF-4EFA-A808-2E62F5B9BF6B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3A1D022E-6F79-4E66-AB34-B9D20E7EDD78}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -925,7 +925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EE2903-FC55-46D2-B322-9AD334A84B5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9780200-4425-4B7E-A752-5BD69D04296F}">
   <dimension ref="B3:L65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
